--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T08:45:50+00:00</t>
+    <t>2026-09-14T09:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:32:54+00:00</t>
+    <t>2026-09-15T09:11:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T09:11:17+00:00</t>
+    <t>2026-09-16T09:03:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:03:59+00:00</t>
+    <t>2026-09-18T08:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:45:46+00:00</t>
+    <t>2026-09-19T08:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-19T08:31:43+00:00</t>
+    <t>2026-09-20T09:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T09:02:38+00:00</t>
+    <t>2026-09-21T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T09:33:49+00:00</t>
+    <t>2026-09-22T09:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T09:02:23+00:00</t>
+    <t>2026-09-23T09:05:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:05:06+00:00</t>
+    <t>2026-09-26T09:04:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-26T09:04:06+00:00</t>
+    <t>2026-09-27T09:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/main/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-27T09:48:22+00:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
